--- a/CF_ESP/CATALOGOS/Anexo 5.xlsx
+++ b/CF_ESP/CATALOGOS/Anexo 5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4c8ce57d2d00b7c/Documentos/Stagged/ION/Analisis/CF_ESP/CATALOGOS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/65a63616e5f6ec42/Desktop/DOCUMENTOS_IMPERA/ION/CF_ESP/CATALOGOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A3D3161-C441-4726-A868-40A54CBBC912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{893E039D-04E2-47EA-8EE3-79429A4098D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="29920" windowHeight="16020" xr2:uid="{D0632C80-5BDC-486B-9FCE-6C399756B192}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{31059E68-A8D2-4BA6-A5B9-583F9AEAB27E}"/>
   </bookViews>
   <sheets>
     <sheet name="Anexo 5" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t>Anexo 5</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>CLAVE</t>
   </si>
@@ -62,9 +59,6 @@
     <t>Retail funding, insured by IPAB, with transactional relationship</t>
   </si>
   <si>
-    <t>con relacion transaccional ?</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -72,9 +66,6 @@
   </si>
   <si>
     <t>Retail funding, insured by IPAB, no transactional relationship</t>
-  </si>
-  <si>
-    <t>sin relacion transaccional?</t>
   </si>
   <si>
     <t>3</t>
@@ -144,7 +135,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,38 +144,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -258,28 +229,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -292,8 +253,7 @@
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -625,147 +585,124 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5E23C3D-E08B-4112-8BF6-F1A607B74A6F}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC680EF7-16FD-42C0-8059-251DAC6696B0}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="69.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.81640625" customWidth="1"/>
-    <col min="3" max="3" width="196.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="144.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="175.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6"/>
-    </row>
-    <row r="3" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="9" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
